--- a/workspace/framework_paper/map-bf/map-bf-10/map-bf-10_times_success.xlsx
+++ b/workspace/framework_paper/map-bf/map-bf-10/map-bf-10_times_success.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>bf</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>bf-seq</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -478,6 +483,9 @@
       <c r="H2" t="n">
         <v>1.894676554203033</v>
       </c>
+      <c r="I2" t="n">
+        <v>9.126702718734741</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -504,6 +512,9 @@
       <c r="H3" t="n">
         <v>2.115987896323204</v>
       </c>
+      <c r="I3" t="n">
+        <v>23.87136682271957</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -530,6 +541,9 @@
       <c r="H4" t="n">
         <v>2.168079690933228</v>
       </c>
+      <c r="I4" t="n">
+        <v>13.8283218640089</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -556,6 +570,9 @@
       <c r="H5" t="n">
         <v>1.500013507008553</v>
       </c>
+      <c r="I5" t="n">
+        <v>11.00256102621555</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -582,6 +599,9 @@
       <c r="H6" t="n">
         <v>1.607716554775834</v>
       </c>
+      <c r="I6" t="n">
+        <v>20.26579325382287</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -608,6 +628,9 @@
       <c r="H7" t="n">
         <v>1.632443823892137</v>
       </c>
+      <c r="I7" t="n">
+        <v>15.13017826948477</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -634,6 +657,9 @@
       <c r="H8" t="n">
         <v>1.421463790264997</v>
       </c>
+      <c r="I8" t="n">
+        <v>15.62802786380053</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -660,6 +686,9 @@
       <c r="H9" t="n">
         <v>1.06131775748162</v>
       </c>
+      <c r="I9" t="n">
+        <v>8.812167871566047</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -686,6 +715,9 @@
       <c r="H10" t="n">
         <v>0.5585818524871554</v>
       </c>
+      <c r="I10" t="n">
+        <v>1.61445156697716</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -712,6 +744,9 @@
       <c r="H11" t="n">
         <v>0.7705184526386715</v>
       </c>
+      <c r="I11" t="n">
+        <v>13.36201852489085</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -738,6 +773,9 @@
       <c r="H12" t="n">
         <v>0.5666655637323856</v>
       </c>
+      <c r="I12" t="n">
+        <v>2.117831690981984</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -764,6 +802,9 @@
       <c r="H13" t="n">
         <v>0.5994012583243219</v>
       </c>
+      <c r="I13" t="n">
+        <v>2.070745895175557</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -790,6 +831,9 @@
       <c r="H14" t="n">
         <v>0.5336612392412988</v>
       </c>
+      <c r="I14" t="n">
+        <v>1.238038969667334</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -815,6 +859,9 @@
       </c>
       <c r="H15" t="n">
         <v>0.4378692923407805</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.740968532860279</v>
       </c>
     </row>
     <row r="16">
@@ -836,6 +883,9 @@
       <c r="H16" t="n">
         <v>0.4397478480088083</v>
       </c>
+      <c r="I16" t="n">
+        <v>1.673759571227588</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -856,6 +906,9 @@
       <c r="H17" t="n">
         <v>0.5321510657668114</v>
       </c>
+      <c r="I17" t="n">
+        <v>2.377501337064637</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -876,6 +929,9 @@
       <c r="H18" t="n">
         <v>0.437596939942416</v>
       </c>
+      <c r="I18" t="n">
+        <v>1.175208760096746</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -896,6 +952,9 @@
       <c r="H19" t="n">
         <v>0.6430877061451182</v>
       </c>
+      <c r="I19" t="n">
+        <v>2.316562896265703</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -916,6 +975,9 @@
       <c r="H20" t="n">
         <v>0.7855170061190923</v>
       </c>
+      <c r="I20" t="n">
+        <v>2.840277025103569</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -936,6 +998,9 @@
       <c r="H21" t="n">
         <v>0.5429465892640027</v>
       </c>
+      <c r="I21" t="n">
+        <v>2.406747755679217</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
